--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios124.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios124.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.81124754310822</v>
+        <v>34.88194079249295</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.30931574544448</v>
+        <v>33.15113306484162</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.16096832076008</v>
+        <v>25.40506536575331</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.59713512173497</v>
+        <v>30.74316087460538</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.10683352323325</v>
+        <v>32.4562445915538</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.91891401588097</v>
+        <v>30.90517152931622</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32.37620791745756</v>
+        <v>34.3803910617565</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.02373911851042</v>
+        <v>32.89667085910177</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.45949899128703</v>
+        <v>25.12516771508507</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.65104421285681</v>
+        <v>30.71035470571593</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.53011656085197</v>
+        <v>31.27586689648772</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30.47552560368331</v>
+        <v>31.30973493666189</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32.70122286277999</v>
+        <v>34.51991552534047</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.10723100765465</v>
+        <v>33.13537677264207</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28.15500639822899</v>
+        <v>25.12079584193003</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.24808897339387</v>
+        <v>30.43166384536256</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.63312435323784</v>
+        <v>31.77201865306234</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30.24069305693786</v>
+        <v>31.00573030964837</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32.43524745580911</v>
+        <v>34.954246235179</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.25893551032041</v>
+        <v>33.22933901769593</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28.24985259964706</v>
+        <v>24.782322056269</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.27920916535204</v>
+        <v>30.87524376168458</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.10565972939916</v>
+        <v>31.76678409782425</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.35903095455533</v>
+        <v>31.08919525759352</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.47061150065653</v>
+        <v>26.17367816698499</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30.12433560327193</v>
+        <v>29.61118981152926</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30.94491509795276</v>
+        <v>29.96105283602877</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.12392120935565</v>
+        <v>22.79911277227946</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31.5818078488546</v>
+        <v>26.96989866972044</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.44104994753926</v>
+        <v>18.05335851802283</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.16816113532641</v>
+        <v>26.01838183220007</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>30.21319982151102</v>
+        <v>29.98496889744596</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.18803276123437</v>
+        <v>30.09401346621802</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.47277816547091</v>
+        <v>23.02453953302593</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32.32070330669757</v>
+        <v>26.61267293273503</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24.75031095224393</v>
+        <v>18.18370188155594</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31.38773751939545</v>
+        <v>26.06272152860327</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>29.97428287434502</v>
+        <v>29.74865383416386</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>31.08561136078287</v>
+        <v>30.04498832084879</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27.97781657534463</v>
+        <v>22.54434894200682</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>32.14927684841976</v>
+        <v>26.04945302502296</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>24.5848894321725</v>
+        <v>18.29367423069531</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31.55674953720092</v>
+        <v>26.6327318310121</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30.74190701694813</v>
+        <v>29.84643015384101</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>31.05755233061704</v>
+        <v>30.3015597474106</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28.17152628846243</v>
+        <v>23.14735205905284</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.26702148377129</v>
+        <v>27.26459534675661</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24.69049725620035</v>
+        <v>18.24904412950099</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios124.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios124.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
